--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -405,6 +405,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -421,112 +452,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -542,8 +467,83 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +558,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,7 +570,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,13 +606,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,31 +708,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -636,49 +726,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,54 +742,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -749,6 +749,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -769,8 +793,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -787,21 +813,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -824,27 +835,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -857,7 +857,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -866,7 +866,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,127 +875,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4632,7 +4632,7 @@
         <v>50</v>
       </c>
       <c r="D25">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H28">
         <v>20</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O28">
         <v>50</v>
@@ -4897,7 +4897,7 @@
         <v>55</v>
       </c>
       <c r="D30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>15</v>
       </c>
       <c r="G30">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H30">
         <v>16</v>
@@ -4950,13 +4950,13 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G31">
         <v>12</v>
@@ -5056,7 +5056,7 @@
         <v>58</v>
       </c>
       <c r="D33">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -8814,20 +8814,20 @@
         <v>1006</v>
       </c>
       <c r="B155">
-        <v>100610</v>
+        <v>1070</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -8838,17 +8838,17 @@
         <v>1006</v>
       </c>
       <c r="B156">
-        <v>100620</v>
+        <v>100610</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8862,20 +8862,20 @@
         <v>1006</v>
       </c>
       <c r="B157">
-        <v>11040</v>
+        <v>100620</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F157">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -8886,11 +8886,11 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>401030</v>
+        <v>11040</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -8899,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -8910,11 +8910,11 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>411040</v>
+        <v>401030</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -8934,11 +8934,11 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>13040</v>
+        <v>411040</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -8958,11 +8958,11 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>13050</v>
+        <v>13040</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D161">
         <v>1</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -391,10 +391,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -405,16 +405,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -430,7 +436,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,38 +466,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -490,28 +480,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -520,8 +488,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -536,14 +513,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +558,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,13 +576,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,13 +594,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,25 +606,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,13 +624,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,79 +738,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,21 +749,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -793,11 +778,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,18 +802,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -849,6 +825,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -857,145 +857,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="G70">
         <v>0</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -391,8 +391,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -405,6 +405,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -414,6 +445,36 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -435,78 +496,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -528,15 +520,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +558,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,25 +600,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -606,7 +624,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,7 +672,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -630,43 +708,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,61 +720,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,11 +752,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,7 +786,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -802,11 +808,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -829,23 +833,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -857,145 +857,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5454,11 +5454,11 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>12090</v>
+        <v>15030</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B15,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>グレイブアクト</v>
       </c>
       <c r="D15">
         <v>41</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -391,10 +391,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -405,9 +405,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -421,10 +467,34 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -437,68 +507,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,9 +527,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -528,22 +543,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +558,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,7 +594,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,7 +630,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,7 +654,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,13 +678,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -630,115 +726,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,6 +778,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -829,26 +849,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -857,16 +857,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,127 +875,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4612,7 +4612,7 @@
         <v>40</v>
       </c>
       <c r="O24">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P24">
         <v>70</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>雷</t>
   </si>
   <si>
-    <t>Wolf</t>
+    <t>Slime</t>
   </si>
   <si>
     <t>炎</t>
@@ -391,10 +391,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -402,6 +402,13 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -420,24 +427,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,37 +451,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -490,38 +458,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -541,9 +479,71 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +558,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,7 +582,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,19 +708,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -606,139 +726,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,26 +778,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -849,6 +829,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -857,16 +857,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,127 +875,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -71,25 +71,25 @@
     <t>SpdGrowth</t>
   </si>
   <si>
-    <t>Jelslime</t>
+    <t>Slime</t>
   </si>
   <si>
     <t>氷</t>
   </si>
   <si>
-    <t>Cursed</t>
+    <t>Beholder</t>
   </si>
   <si>
     <t>闇</t>
   </si>
   <si>
-    <t>Bee</t>
+    <t>BattleBee</t>
   </si>
   <si>
     <t>雷</t>
   </si>
   <si>
-    <t>Slime</t>
+    <t>Werewolf</t>
   </si>
   <si>
     <t>炎</t>
@@ -98,37 +98,37 @@
     <t>Crow</t>
   </si>
   <si>
-    <t>Nameless</t>
-  </si>
-  <si>
-    <t>Seacher</t>
-  </si>
-  <si>
-    <t>Shiled</t>
-  </si>
-  <si>
-    <t>Dryad</t>
-  </si>
-  <si>
-    <t>Scorpion</t>
-  </si>
-  <si>
-    <t>Squid</t>
-  </si>
-  <si>
-    <t>Creeper</t>
-  </si>
-  <si>
-    <t>Imp</t>
+    <t>BishopKnight</t>
+  </si>
+  <si>
+    <t>Specter</t>
+  </si>
+  <si>
+    <t>TurtleShell</t>
+  </si>
+  <si>
+    <t>MonsterPlant</t>
+  </si>
+  <si>
+    <t>StingRay</t>
+  </si>
+  <si>
+    <t>Fishman</t>
+  </si>
+  <si>
+    <t>BlackKnight</t>
+  </si>
+  <si>
+    <t>Cyclops</t>
   </si>
   <si>
     <t>白</t>
   </si>
   <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>Sword</t>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>NagaWizard</t>
   </si>
   <si>
     <t>Ammon</t>
@@ -239,7 +239,7 @@
     <t>Text</t>
   </si>
   <si>
-    <t>ネレイドジェム</t>
+    <t>スライム</t>
   </si>
   <si>
     <t>カースド</t>
@@ -254,34 +254,34 @@
     <t>クロウ</t>
   </si>
   <si>
-    <t>ネームレス</t>
-  </si>
-  <si>
-    <t>サーチャー</t>
-  </si>
-  <si>
-    <t>シールド</t>
+    <t>ビショップ</t>
+  </si>
+  <si>
+    <t>スペクター</t>
+  </si>
+  <si>
+    <t>タートルシェル</t>
   </si>
   <si>
     <t>ドライアド</t>
   </si>
   <si>
-    <t>スコーピオン</t>
-  </si>
-  <si>
-    <t>スクイッド</t>
-  </si>
-  <si>
-    <t>クリーパー</t>
-  </si>
-  <si>
-    <t>インプ</t>
-  </si>
-  <si>
-    <t>ゴーストアーマー</t>
-  </si>
-  <si>
-    <t>ソード</t>
+    <t>スティングレイ</t>
+  </si>
+  <si>
+    <t>フィッシャーマン</t>
+  </si>
+  <si>
+    <t>ブラックナイト</t>
+  </si>
+  <si>
+    <t>サイクロプス</t>
+  </si>
+  <si>
+    <t>スケルトン</t>
+  </si>
+  <si>
+    <t>リザード</t>
   </si>
   <si>
     <t>アモン</t>
@@ -391,10 +391,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -405,8 +405,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,9 +420,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,9 +442,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -450,30 +465,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,8 +518,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -533,17 +542,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,25 +558,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,19 +570,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,67 +642,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,13 +666,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,37 +732,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,17 +752,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,7 +782,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -834,18 +830,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -857,43 +857,43 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -905,97 +905,97 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="147">
   <si>
     <t>Id</t>
   </si>
@@ -77,90 +77,132 @@
     <t>氷</t>
   </si>
   <si>
-    <t>Beholder</t>
+    <t>Bat</t>
   </si>
   <si>
     <t>闇</t>
   </si>
   <si>
-    <t>BattleBee</t>
+    <t>Hornet</t>
   </si>
   <si>
     <t>雷</t>
   </si>
   <si>
+    <t>Spider</t>
+  </si>
+  <si>
+    <t>炎</t>
+  </si>
+  <si>
+    <t>Rat</t>
+  </si>
+  <si>
+    <t>Willowisp</t>
+  </si>
+  <si>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>Orc</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>Imp</t>
+  </si>
+  <si>
+    <t>Gayzer</t>
+  </si>
+  <si>
+    <t>Puppet</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Cockatrice</t>
+  </si>
+  <si>
+    <t>Sahagin</t>
+  </si>
+  <si>
     <t>Werewolf</t>
   </si>
   <si>
-    <t>炎</t>
-  </si>
-  <si>
-    <t>Crow</t>
-  </si>
-  <si>
-    <t>BishopKnight</t>
-  </si>
-  <si>
-    <t>Specter</t>
-  </si>
-  <si>
-    <t>TurtleShell</t>
-  </si>
-  <si>
-    <t>MonsterPlant</t>
-  </si>
-  <si>
-    <t>StingRay</t>
-  </si>
-  <si>
-    <t>Fishman</t>
-  </si>
-  <si>
-    <t>BlackKnight</t>
-  </si>
-  <si>
-    <t>Cyclops</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>Skeleton</t>
-  </si>
-  <si>
-    <t>NagaWizard</t>
-  </si>
-  <si>
-    <t>Ammon</t>
+    <t>Behemoth</t>
   </si>
   <si>
     <t>2ボス</t>
   </si>
   <si>
-    <t>Berith</t>
+    <t>Minotaur</t>
   </si>
   <si>
     <t>5ボス</t>
   </si>
   <si>
-    <t>Paimon</t>
+    <t>Windspirit</t>
   </si>
   <si>
     <t>3ボス</t>
   </si>
   <si>
-    <t>Andras</t>
+    <t>Evilking</t>
   </si>
   <si>
     <t>4ボス</t>
   </si>
   <si>
-    <t>Bifrons</t>
+    <t>Kerberos</t>
   </si>
   <si>
     <t>6ボス</t>
   </si>
   <si>
+    <t>Garuda</t>
+  </si>
+  <si>
+    <t>Dragon</t>
+  </si>
+  <si>
+    <t>Lamia</t>
+  </si>
+  <si>
+    <t>Puppet_E</t>
+  </si>
+  <si>
+    <t>Vampire</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>Slime_L</t>
+  </si>
+  <si>
+    <t>Demon_E</t>
+  </si>
+  <si>
+    <t>Chimera</t>
+  </si>
+  <si>
     <t>Cyaegha</t>
   </si>
   <si>
@@ -242,67 +284,103 @@
     <t>スライム</t>
   </si>
   <si>
-    <t>カースド</t>
-  </si>
-  <si>
-    <t>ビー</t>
-  </si>
-  <si>
-    <t>ウルフ</t>
-  </si>
-  <si>
-    <t>クロウ</t>
-  </si>
-  <si>
-    <t>ビショップ</t>
-  </si>
-  <si>
-    <t>スペクター</t>
-  </si>
-  <si>
-    <t>タートルシェル</t>
-  </si>
-  <si>
-    <t>ドライアド</t>
-  </si>
-  <si>
-    <t>スティングレイ</t>
-  </si>
-  <si>
-    <t>フィッシャーマン</t>
-  </si>
-  <si>
-    <t>ブラックナイト</t>
-  </si>
-  <si>
-    <t>サイクロプス</t>
+    <t>バット</t>
+  </si>
+  <si>
+    <t>ホーネット</t>
+  </si>
+  <si>
+    <t>スパイダー</t>
+  </si>
+  <si>
+    <t>ビッグラット</t>
+  </si>
+  <si>
+    <t>ウィスプ</t>
+  </si>
+  <si>
+    <t>スネーク</t>
+  </si>
+  <si>
+    <t>スコーピオン</t>
+  </si>
+  <si>
+    <t>ゼリーフィッシュ</t>
+  </si>
+  <si>
+    <t>マッドプラント</t>
+  </si>
+  <si>
+    <t>ゴースト</t>
   </si>
   <si>
     <t>スケルトン</t>
   </si>
   <si>
-    <t>リザード</t>
-  </si>
-  <si>
-    <t>アモン</t>
-  </si>
-  <si>
-    <t>ベリト</t>
-  </si>
-  <si>
-    <t>パイモン</t>
-  </si>
-  <si>
-    <t>アンドラス</t>
-  </si>
-  <si>
-    <t>ビフロンス</t>
-  </si>
-  <si>
-    <t>アイホート</t>
-  </si>
-  <si>
-    <t>ビヤーキー</t>
+    <t>オーク</t>
+  </si>
+  <si>
+    <t>インプ</t>
+  </si>
+  <si>
+    <t>ゲイザー</t>
+  </si>
+  <si>
+    <t>パペット</t>
+  </si>
+  <si>
+    <t>ゾンビ</t>
+  </si>
+  <si>
+    <t>コカトリス</t>
+  </si>
+  <si>
+    <t>サハギン</t>
+  </si>
+  <si>
+    <t>ウェアウルフ</t>
+  </si>
+  <si>
+    <t>ベヒーモス</t>
+  </si>
+  <si>
+    <t>ミノタウロス</t>
+  </si>
+  <si>
+    <t>シルフ</t>
+  </si>
+  <si>
+    <t>イヴィルキング</t>
+  </si>
+  <si>
+    <t>ケルベロス</t>
+  </si>
+  <si>
+    <t>ガルーダ</t>
+  </si>
+  <si>
+    <t>ドラゴン</t>
+  </si>
+  <si>
+    <t>ラミア</t>
+  </si>
+  <si>
+    <t>コピーパペット</t>
+  </si>
+  <si>
+    <t>ヴァンパイア</t>
+  </si>
+  <si>
+    <t>デス</t>
+  </si>
+  <si>
+    <t>エナメルスライム</t>
+  </si>
+  <si>
+    <t>デーモン</t>
+  </si>
+  <si>
+    <t>キメラ</t>
   </si>
   <si>
     <t>アンリマユ</t>
@@ -393,8 +471,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -402,6 +480,51 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -414,7 +537,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,65 +590,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -502,19 +604,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -528,22 +621,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,7 +636,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,7 +660,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,7 +702,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,25 +720,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,7 +732,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -636,7 +756,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,31 +780,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,61 +810,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,11 +832,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -778,11 +869,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -804,24 +901,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -830,22 +923,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -857,145 +935,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3338,7 +3416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="7.63636363636364" customWidth="1"/>
@@ -4194,142 +4272,142 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:17">
       <c r="A17">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
         <v>12</v>
       </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17">
-        <v>18</v>
-      </c>
       <c r="I17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="O17">
         <v>40</v>
       </c>
       <c r="P17">
-        <v>20</v>
-      </c>
-      <c r="R17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18">
-        <v>102</v>
-      </c>
-      <c r="B18">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18">
         <v>38</v>
       </c>
-      <c r="D18">
-        <v>50</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>6</v>
       </c>
       <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>11</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>60</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>80</v>
+      </c>
+      <c r="O18">
+        <v>20</v>
+      </c>
+      <c r="P18">
+        <v>60</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18">
-        <v>12</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>60</v>
-      </c>
-      <c r="O18">
-        <v>35</v>
-      </c>
-      <c r="P18">
-        <v>40</v>
-      </c>
-      <c r="R18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19">
-        <v>103</v>
-      </c>
       <c r="B19">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+      <c r="H19">
         <v>14</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19">
-        <v>22</v>
       </c>
       <c r="I19">
         <v>6</v>
       </c>
       <c r="J19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -4344,145 +4422,145 @@
         <v>50</v>
       </c>
       <c r="O19">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="P19">
-        <v>30</v>
-      </c>
-      <c r="R19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>40</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>12</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <v>11</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>90</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>80</v>
+      </c>
+      <c r="O20">
+        <v>20</v>
+      </c>
+      <c r="P20">
+        <v>40</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>31</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>11</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>50</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>60</v>
+      </c>
+      <c r="O21">
+        <v>20</v>
+      </c>
+      <c r="P21">
         <v>70</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20">
-        <v>16</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20">
-        <v>12</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>50</v>
-      </c>
-      <c r="O20">
-        <v>25</v>
-      </c>
-      <c r="P20">
-        <v>50</v>
-      </c>
-      <c r="R20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21">
-        <v>105</v>
-      </c>
-      <c r="B21">
-        <v>105</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21">
-        <v>100</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>25</v>
-      </c>
-      <c r="H21">
-        <v>13</v>
-      </c>
-      <c r="I21">
-        <v>6</v>
-      </c>
-      <c r="J21">
-        <v>12</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>70</v>
-      </c>
-      <c r="O21">
-        <v>50</v>
-      </c>
-      <c r="P21">
-        <v>15</v>
-      </c>
-      <c r="R21" t="s">
-        <v>45</v>
+      <c r="Q21" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="B22">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -4494,63 +4572,60 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O22">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P22">
-        <v>60</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>19</v>
-      </c>
-      <c r="R22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
+        <v>20</v>
+      </c>
+      <c r="R22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
-        <v>1001</v>
+        <v>102</v>
       </c>
       <c r="B23">
-        <v>1001</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G23">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4559,186 +4634,186 @@
         <v>60</v>
       </c>
       <c r="O23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P23">
-        <v>35</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
+        <v>40</v>
+      </c>
+      <c r="R23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
-        <v>1002</v>
+        <v>103</v>
       </c>
       <c r="B24">
-        <v>1002</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D24">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
+        <v>50</v>
+      </c>
+      <c r="O24">
+        <v>30</v>
+      </c>
+      <c r="P24">
+        <v>30</v>
+      </c>
+      <c r="R24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25">
+        <v>104</v>
+      </c>
+      <c r="B25">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25">
+        <v>70</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>12</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>50</v>
+      </c>
+      <c r="O25">
+        <v>25</v>
+      </c>
+      <c r="P25">
+        <v>50</v>
+      </c>
+      <c r="R25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26">
+        <v>105</v>
+      </c>
+      <c r="B26">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26">
+        <v>13</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>12</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>70</v>
+      </c>
+      <c r="O26">
+        <v>50</v>
+      </c>
+      <c r="P26">
+        <v>15</v>
+      </c>
+      <c r="R26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27">
+        <v>106</v>
+      </c>
+      <c r="B27">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
         <v>40</v>
-      </c>
-      <c r="O24">
-        <v>25</v>
-      </c>
-      <c r="P24">
-        <v>70</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25">
-        <v>1003</v>
-      </c>
-      <c r="B25">
-        <v>1003</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25">
-        <v>35</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>17</v>
-      </c>
-      <c r="G25">
-        <v>12</v>
-      </c>
-      <c r="H25">
-        <v>9</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>85</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>25</v>
-      </c>
-      <c r="O25">
-        <v>40</v>
-      </c>
-      <c r="P25">
-        <v>25</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26">
-        <v>1004</v>
-      </c>
-      <c r="B26">
-        <v>1004</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26">
-        <v>32</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>7</v>
-      </c>
-      <c r="H26">
-        <v>21</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>85</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>35</v>
-      </c>
-      <c r="O26">
-        <v>15</v>
-      </c>
-      <c r="P26">
-        <v>30</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27">
-        <v>1005</v>
-      </c>
-      <c r="B27">
-        <v>1005</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27">
-        <v>29</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4747,157 +4822,157 @@
         <v>12</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H27">
+        <v>18</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
         <v>12</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
+        <v>80</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>70</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>30</v>
       </c>
       <c r="O27">
         <v>40</v>
       </c>
       <c r="P27">
-        <v>45</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+        <v>20</v>
+      </c>
+      <c r="R27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28">
-        <v>1006</v>
+        <v>107</v>
       </c>
       <c r="B28">
-        <v>1006</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28">
+        <v>18</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>12</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>60</v>
+      </c>
+      <c r="O28">
+        <v>35</v>
+      </c>
+      <c r="P28">
+        <v>40</v>
+      </c>
+      <c r="R28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29">
+        <v>108</v>
+      </c>
+      <c r="B29">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
         <v>53</v>
       </c>
-      <c r="D28">
+      <c r="D29">
+        <v>70</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>22</v>
+      </c>
+      <c r="I29">
+        <v>6</v>
+      </c>
+      <c r="J29">
+        <v>12</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>50</v>
+      </c>
+      <c r="O29">
         <v>30</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>20</v>
-      </c>
-      <c r="G28">
-        <v>19</v>
-      </c>
-      <c r="H28">
-        <v>20</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>40</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>50</v>
-      </c>
-      <c r="O28">
-        <v>50</v>
-      </c>
-      <c r="P28">
-        <v>50</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29">
-        <v>1007</v>
-      </c>
-      <c r="B29">
-        <v>1007</v>
-      </c>
-      <c r="C29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>22</v>
-      </c>
-      <c r="G29">
-        <v>18</v>
-      </c>
-      <c r="H29">
-        <v>16</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>65</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>45</v>
-      </c>
-      <c r="O29">
-        <v>40</v>
       </c>
       <c r="P29">
         <v>30</v>
       </c>
-      <c r="Q29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
-        <v>1008</v>
+        <v>109</v>
       </c>
       <c r="B30">
-        <v>1008</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4906,196 +4981,941 @@
         <v>15</v>
       </c>
       <c r="G30">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>16</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>50</v>
+      </c>
+      <c r="O30">
+        <v>25</v>
+      </c>
+      <c r="P30">
+        <v>50</v>
+      </c>
+      <c r="R30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31">
+        <v>110</v>
+      </c>
+      <c r="B31">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>12</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="H31">
+        <v>13</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>70</v>
+      </c>
+      <c r="O31">
+        <v>50</v>
+      </c>
+      <c r="P31">
+        <v>15</v>
+      </c>
+      <c r="R31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32">
+        <v>111</v>
+      </c>
+      <c r="B32">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32">
+        <v>40</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>12</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>18</v>
+      </c>
+      <c r="I32">
+        <v>5</v>
+      </c>
+      <c r="J32">
+        <v>12</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>80</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>70</v>
+      </c>
+      <c r="O32">
         <v>40</v>
       </c>
-      <c r="O30">
-        <v>60</v>
-      </c>
-      <c r="P30">
-        <v>35</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31">
-        <v>1009</v>
-      </c>
-      <c r="B31">
-        <v>1009</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31">
-        <v>34</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>25</v>
-      </c>
-      <c r="G31">
-        <v>12</v>
-      </c>
-      <c r="H31">
-        <v>24</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>25</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>65</v>
-      </c>
-      <c r="O31">
-        <v>30</v>
-      </c>
-      <c r="P31">
+      <c r="P32">
+        <v>20</v>
+      </c>
+      <c r="R32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33">
+        <v>112</v>
+      </c>
+      <c r="B33">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33">
         <v>50</v>
       </c>
-      <c r="Q31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32">
-        <v>1010</v>
-      </c>
-      <c r="B32">
-        <v>1010</v>
-      </c>
-      <c r="C32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32">
-        <v>30</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>17</v>
-      </c>
-      <c r="G32">
-        <v>7</v>
-      </c>
-      <c r="H32">
-        <v>31</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>45</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>30</v>
-      </c>
-      <c r="O32">
-        <v>20</v>
-      </c>
-      <c r="P32">
-        <v>75</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33">
-        <v>1011</v>
-      </c>
-      <c r="B33">
-        <v>1011</v>
-      </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33">
-        <v>33</v>
-      </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G33">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>18</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>60</v>
+      </c>
+      <c r="O33">
+        <v>35</v>
+      </c>
+      <c r="P33">
+        <v>40</v>
+      </c>
+      <c r="R33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34">
+        <v>113</v>
+      </c>
+      <c r="B34">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34">
+        <v>70</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>14</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>22</v>
+      </c>
+      <c r="I34">
+        <v>6</v>
+      </c>
+      <c r="J34">
+        <v>12</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>50</v>
+      </c>
+      <c r="O34">
+        <v>30</v>
+      </c>
+      <c r="P34">
+        <v>30</v>
+      </c>
+      <c r="R34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35">
+        <v>114</v>
+      </c>
+      <c r="B35">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35">
+        <v>70</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>15</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>16</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>12</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>100</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>50</v>
+      </c>
+      <c r="O35">
+        <v>25</v>
+      </c>
+      <c r="P35">
+        <v>50</v>
+      </c>
+      <c r="R35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36">
+        <v>201</v>
+      </c>
+      <c r="B36">
+        <v>201</v>
+      </c>
+      <c r="C36" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>20</v>
+      </c>
+      <c r="G36">
+        <v>20</v>
+      </c>
+      <c r="H36">
+        <v>20</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>12</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>120</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>80</v>
+      </c>
+      <c r="O36">
+        <v>60</v>
+      </c>
+      <c r="P36">
+        <v>60</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>19</v>
+      </c>
+      <c r="R36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37">
+        <v>1001</v>
+      </c>
+      <c r="B37">
+        <v>1001</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37">
+        <v>39</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>30</v>
+      </c>
+      <c r="G37">
+        <v>15</v>
+      </c>
+      <c r="H37">
+        <v>15</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>55</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>60</v>
+      </c>
+      <c r="O37">
+        <v>30</v>
+      </c>
+      <c r="P37">
+        <v>35</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38">
+        <v>1002</v>
+      </c>
+      <c r="B38">
+        <v>1002</v>
+      </c>
+      <c r="C38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38">
+        <v>29</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>21</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>28</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>60</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>40</v>
+      </c>
+      <c r="O38">
+        <v>25</v>
+      </c>
+      <c r="P38">
+        <v>70</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39">
+        <v>1003</v>
+      </c>
+      <c r="B39">
+        <v>1003</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39">
+        <v>35</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>17</v>
+      </c>
+      <c r="G39">
+        <v>12</v>
+      </c>
+      <c r="H39">
+        <v>9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>85</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>25</v>
+      </c>
+      <c r="O39">
+        <v>40</v>
+      </c>
+      <c r="P39">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40">
+        <v>1004</v>
+      </c>
+      <c r="B40">
+        <v>1004</v>
+      </c>
+      <c r="C40" t="s">
         <v>65</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
+      <c r="D40">
+        <v>32</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>7</v>
+      </c>
+      <c r="H40">
+        <v>21</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>85</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>35</v>
+      </c>
+      <c r="O40">
+        <v>15</v>
+      </c>
+      <c r="P40">
+        <v>30</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41">
+        <v>1005</v>
+      </c>
+      <c r="B41">
+        <v>1005</v>
+      </c>
+      <c r="C41" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41">
+        <v>29</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+      <c r="H41">
+        <v>12</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>70</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>30</v>
+      </c>
+      <c r="O41">
         <v>40</v>
       </c>
-      <c r="O33">
+      <c r="P41">
+        <v>45</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42">
+        <v>1006</v>
+      </c>
+      <c r="B42">
+        <v>1006</v>
+      </c>
+      <c r="C42" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42">
+        <v>30</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>20</v>
+      </c>
+      <c r="G42">
+        <v>19</v>
+      </c>
+      <c r="H42">
+        <v>20</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>40</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>50</v>
+      </c>
+      <c r="O42">
+        <v>50</v>
+      </c>
+      <c r="P42">
+        <v>50</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43">
+        <v>1007</v>
+      </c>
+      <c r="B43">
+        <v>1007</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43">
+        <v>40</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>22</v>
+      </c>
+      <c r="G43">
+        <v>18</v>
+      </c>
+      <c r="H43">
+        <v>16</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>65</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>45</v>
+      </c>
+      <c r="O43">
+        <v>40</v>
+      </c>
+      <c r="P43">
+        <v>30</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44">
+        <v>1008</v>
+      </c>
+      <c r="B44">
+        <v>1008</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44">
+        <v>37</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>15</v>
+      </c>
+      <c r="G44">
+        <v>21</v>
+      </c>
+      <c r="H44">
+        <v>16</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>80</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>40</v>
+      </c>
+      <c r="O44">
+        <v>60</v>
+      </c>
+      <c r="P44">
+        <v>35</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45">
+        <v>1009</v>
+      </c>
+      <c r="B45">
+        <v>1009</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45">
+        <v>34</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>25</v>
       </c>
-      <c r="P33">
+      <c r="G45">
+        <v>12</v>
+      </c>
+      <c r="H45">
+        <v>24</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>25</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>65</v>
+      </c>
+      <c r="O45">
         <v>30</v>
       </c>
-      <c r="Q33" t="s">
-        <v>48</v>
+      <c r="P45">
+        <v>50</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46">
+        <v>1010</v>
+      </c>
+      <c r="B46">
+        <v>1010</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>17</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>31</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>45</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>30</v>
+      </c>
+      <c r="O46">
+        <v>20</v>
+      </c>
+      <c r="P46">
+        <v>75</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47">
+        <v>1011</v>
+      </c>
+      <c r="B47">
+        <v>1011</v>
+      </c>
+      <c r="C47" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47">
+        <v>33</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>18</v>
+      </c>
+      <c r="G47">
+        <v>17</v>
+      </c>
+      <c r="H47">
+        <v>18</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>65</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>40</v>
+      </c>
+      <c r="O47">
+        <v>25</v>
+      </c>
+      <c r="P47">
+        <v>30</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5116,25 +5936,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -10071,25 +10891,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -10377,7 +11197,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="13.5454545454545" customWidth="1"/>
@@ -10388,7 +11208,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -10396,7 +11216,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -10404,7 +11224,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -10412,7 +11232,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -10420,7 +11240,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10428,7 +11248,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10436,7 +11256,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10444,7 +11264,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10452,7 +11272,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10460,7 +11280,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10468,7 +11288,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10476,7 +11296,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10484,7 +11304,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10492,7 +11312,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10500,7 +11320,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -10508,215 +11328,311 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>102</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>103</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>104</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>105</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
         <v>106</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
         <v>107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>301</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>1001</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>1002</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>1003</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>1004</v>
+        <v>114</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>1005</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>1006</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>1007</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>1008</v>
+        <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>1009</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>1010</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
+        <v>207</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>301</v>
+      </c>
+      <c r="B43" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>1001</v>
+      </c>
+      <c r="B44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>1002</v>
+      </c>
+      <c r="B45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>1003</v>
+      </c>
+      <c r="B46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>1004</v>
+      </c>
+      <c r="B47" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>1005</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>1006</v>
+      </c>
+      <c r="B49" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>1007</v>
+      </c>
+      <c r="B50" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>1008</v>
+      </c>
+      <c r="B51" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>1009</v>
+      </c>
+      <c r="B52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>1010</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
         <v>1011</v>
       </c>
-      <c r="B42" t="s">
-        <v>111</v>
+      <c r="B54" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -10733,7 +11649,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -10741,7 +11657,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -10749,7 +11665,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -10757,7 +11673,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -10765,7 +11681,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -10773,7 +11689,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -10781,7 +11697,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -10789,7 +11705,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -10797,7 +11713,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -469,10 +469,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -483,8 +483,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,31 +513,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -536,8 +535,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,8 +565,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -567,15 +582,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -590,21 +613,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -612,18 +620,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -636,7 +636,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,7 +654,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,7 +666,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,13 +738,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,133 +810,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -834,7 +834,66 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -855,36 +914,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -898,35 +927,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -935,19 +935,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -956,124 +956,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3488,19 +3488,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>8</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>4</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -469,10 +469,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -484,44 +484,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -535,14 +506,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -550,14 +513,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -573,9 +528,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -589,16 +543,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -613,6 +582,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -620,10 +612,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -636,7 +636,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,7 +738,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,31 +780,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -696,103 +804,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,19 +816,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,6 +827,60 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -850,50 +904,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -912,21 +927,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -935,145 +935,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1183,7 +1183,7 @@
             <v>1</v>
           </cell>
           <cell r="B3" t="str">
-            <v>攻撃</v>
+            <v>はずす</v>
           </cell>
         </row>
         <row r="4">
@@ -1420,687 +1420,687 @@
         </row>
         <row r="33">
           <cell r="A33">
-            <v>4010</v>
+            <v>3110</v>
           </cell>
           <cell r="B33" t="str">
-            <v>セイントレーザー</v>
+            <v>フリーズランサー</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="B34" t="str">
-            <v>ペネトレイト</v>
+            <v>セイントレーザー</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>4030</v>
+            <v>4020</v>
           </cell>
           <cell r="B35" t="str">
-            <v>ヒーリング</v>
+            <v>ペネトレイト</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>4040</v>
+            <v>4030</v>
           </cell>
           <cell r="B36" t="str">
-            <v>リザイアフォトン</v>
+            <v>ヒーリング</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>4050</v>
+            <v>4040</v>
           </cell>
           <cell r="B37" t="str">
-            <v>べネディクション</v>
+            <v>リザイアフォトン</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>4060</v>
+            <v>4050</v>
           </cell>
           <cell r="B38" t="str">
-            <v>ホーリーグレイス</v>
+            <v>べネディクション</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>4070</v>
+            <v>4060</v>
           </cell>
           <cell r="B39" t="str">
-            <v>キュアエール</v>
+            <v>ホーリーグレイス</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>4080</v>
+            <v>4070</v>
           </cell>
           <cell r="B40" t="str">
-            <v>ラインバリア</v>
+            <v>キュアエール</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>5010</v>
+            <v>4080</v>
           </cell>
           <cell r="B41" t="str">
-            <v>ダークプリズン</v>
+            <v>ラインバリア</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="B42" t="str">
-            <v>ユーサネイジア</v>
+            <v>ダークプリズン</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>5030</v>
+            <v>5020</v>
           </cell>
           <cell r="B43" t="str">
-            <v>ドレインヒール</v>
+            <v>ユーサネイジア</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>5040</v>
+            <v>5030</v>
           </cell>
           <cell r="B44" t="str">
-            <v>アビサルデスペア</v>
+            <v>ドレインヒール</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>5050</v>
+            <v>5040</v>
           </cell>
           <cell r="B45" t="str">
-            <v>ディプラヴィティ</v>
+            <v>アビサルデスペア</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>5060</v>
+            <v>5050</v>
           </cell>
           <cell r="B46" t="str">
-            <v>ダークネス</v>
+            <v>ディプラヴィティ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>5070</v>
+            <v>5060</v>
           </cell>
           <cell r="B47" t="str">
-            <v>シェイディークラウド</v>
+            <v>ダークネス</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>5080</v>
+            <v>5070</v>
           </cell>
           <cell r="B48" t="str">
-            <v>ポイズンブロウ</v>
+            <v>シェイディークラウド</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>10010</v>
+            <v>5080</v>
           </cell>
           <cell r="B49" t="str">
-            <v>アンデッド</v>
+            <v>ポイズンブロウ</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>10020</v>
+            <v>10010</v>
           </cell>
           <cell r="B50" t="str">
-            <v>エアリアル</v>
+            <v>アンデッド</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>10030</v>
+            <v>10020</v>
           </cell>
           <cell r="B51" t="str">
-            <v>悪魔</v>
+            <v>エアリアル</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>10040</v>
+            <v>10030</v>
           </cell>
           <cell r="B52" t="str">
-            <v>クリーチャー</v>
+            <v>悪魔</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>10050</v>
+            <v>10040</v>
           </cell>
           <cell r="B53" t="str">
-            <v>野生の記憶</v>
+            <v>クリーチャー</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>10060</v>
+            <v>10050</v>
           </cell>
           <cell r="B54" t="str">
-            <v>変異生物</v>
+            <v>野生の記憶</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>11010</v>
+            <v>10060</v>
           </cell>
           <cell r="B55" t="str">
-            <v>ウルフソウル</v>
+            <v>変異生物</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>11020</v>
+            <v>11010</v>
           </cell>
           <cell r="B56" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B57" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11040</v>
+            <v>11030</v>
           </cell>
           <cell r="B58" t="str">
-            <v>アクティブギフト</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11050</v>
+            <v>11040</v>
           </cell>
           <cell r="B59" t="str">
-            <v>イグナイテッド</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11060</v>
+            <v>11050</v>
           </cell>
           <cell r="B60" t="str">
-            <v>ライジングファイア</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11070</v>
+            <v>11060</v>
           </cell>
           <cell r="B61" t="str">
-            <v>ルージュバック</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11080</v>
+            <v>11070</v>
           </cell>
           <cell r="B62" t="str">
-            <v>パワーエール</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11090</v>
+            <v>11080</v>
           </cell>
           <cell r="B63" t="str">
-            <v>スレイプニル</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>12010</v>
+            <v>11090</v>
           </cell>
           <cell r="B64" t="str">
-            <v>エクステンション</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B65" t="str">
-            <v>ヘブンリーラック</v>
+            <v>エクステンション</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B66" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B67" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B68" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B69" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B70" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B71" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B72" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B73" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>13020</v>
+            <v>13010</v>
           </cell>
           <cell r="B74" t="str">
-            <v>クイックバリア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>13030</v>
+            <v>13020</v>
           </cell>
           <cell r="B75" t="str">
-            <v>クイックキュア</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>13040</v>
+            <v>13030</v>
           </cell>
           <cell r="B76" t="str">
-            <v>セルフシールド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13050</v>
+            <v>13040</v>
           </cell>
           <cell r="B77" t="str">
-            <v>パッシブジャミング</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13060</v>
+            <v>13050</v>
           </cell>
           <cell r="B78" t="str">
-            <v>サプライカバー</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13070</v>
+            <v>13060</v>
           </cell>
           <cell r="B79" t="str">
-            <v>アシッドラッシュ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13080</v>
+            <v>13070</v>
           </cell>
           <cell r="B80" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13090</v>
+            <v>13080</v>
           </cell>
           <cell r="B81" t="str">
-            <v>アイスセイバー</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>14010</v>
+            <v>13090</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ディバインシールド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>14020</v>
+            <v>14010</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ライフディバイド</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>14030</v>
+            <v>14020</v>
           </cell>
           <cell r="B84" t="str">
-            <v>エイミングスコープ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>14040</v>
+            <v>14030</v>
           </cell>
           <cell r="B85" t="str">
-            <v>リジェネレーション</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>14050</v>
+            <v>14040</v>
           </cell>
           <cell r="B86" t="str">
-            <v>ホープフルアイリス</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14060</v>
+            <v>14050</v>
           </cell>
           <cell r="B87" t="str">
-            <v>パッシブサプライ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14070</v>
+            <v>14060</v>
           </cell>
           <cell r="B88" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14080</v>
+            <v>14070</v>
           </cell>
           <cell r="B89" t="str">
-            <v>クイックヒール</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14090</v>
+            <v>14080</v>
           </cell>
           <cell r="B90" t="str">
-            <v>リレイズ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>15010</v>
+            <v>14090</v>
           </cell>
           <cell r="B91" t="str">
-            <v>イーグルアイ</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>15020</v>
+            <v>15010</v>
           </cell>
           <cell r="B92" t="str">
-            <v>ネヴァーエンド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>15030</v>
+            <v>15020</v>
           </cell>
           <cell r="B93" t="str">
-            <v>グレイブアクト</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>15040</v>
+            <v>15030</v>
           </cell>
           <cell r="B94" t="str">
-            <v>スカルグラッジ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>15050</v>
+            <v>15040</v>
           </cell>
           <cell r="B95" t="str">
-            <v>ネガティブドレイン</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>15060</v>
+            <v>15050</v>
           </cell>
           <cell r="B96" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15070</v>
+            <v>15060</v>
           </cell>
           <cell r="B97" t="str">
-            <v>ジャックポッド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15080</v>
+            <v>15070</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ヒールハント</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15090</v>
+            <v>15080</v>
           </cell>
           <cell r="B99" t="str">
-            <v>クイックカース</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>20010</v>
+            <v>15090</v>
           </cell>
           <cell r="B100" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>100110</v>
+            <v>20010</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ソーイングアームド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B102" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B103" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B104" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B105" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B106" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B107" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B109" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B110" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B111" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B112" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B113" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B114" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B115" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B116" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B117" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B118" t="str">
             <v>バーニングカウンター</v>
@@ -2108,15 +2108,15 @@
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B119" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B120" t="str">
             <v>プロミネンス</v>
@@ -2124,95 +2124,95 @@
         </row>
         <row r="121">
           <cell r="A121">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B121" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B122" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B123" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B124" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B125" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>200220</v>
+            <v>200210</v>
           </cell>
           <cell r="B126" t="str">
-            <v>カタストロフィ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200230</v>
+            <v>200220</v>
           </cell>
           <cell r="B127" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200310</v>
+            <v>200230</v>
           </cell>
           <cell r="B128" t="str">
-            <v>プルガシオン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200320</v>
+            <v>200310</v>
           </cell>
           <cell r="B129" t="str">
-            <v>プリエステス</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200330</v>
+            <v>200320</v>
           </cell>
           <cell r="B130" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200410</v>
+            <v>200330</v>
           </cell>
           <cell r="B131" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200411</v>
+            <v>200410</v>
           </cell>
           <cell r="B132" t="str">
             <v>コウソクテンショウ</v>
@@ -2220,905 +2220,913 @@
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200420</v>
+            <v>200411</v>
           </cell>
           <cell r="B133" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200430</v>
+            <v>200420</v>
           </cell>
           <cell r="B134" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200510</v>
+            <v>200430</v>
           </cell>
           <cell r="B135" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200520</v>
+            <v>200510</v>
           </cell>
           <cell r="B136" t="str">
-            <v>グラウンドゼロ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200530</v>
+            <v>200520</v>
           </cell>
           <cell r="B137" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>201010</v>
+            <v>200530</v>
           </cell>
           <cell r="B138" t="str">
-            <v>カオスペイン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>201020</v>
+            <v>201010</v>
           </cell>
           <cell r="B139" t="str">
-            <v>フォールンワン</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201030</v>
+            <v>201020</v>
           </cell>
           <cell r="B140" t="str">
-            <v>アンリマユ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>300010</v>
+            <v>201030</v>
           </cell>
           <cell r="B141" t="str">
-            <v>ライフブースト</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>300020</v>
+            <v>300010</v>
           </cell>
           <cell r="B142" t="str">
-            <v>スピリットチャージ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300030</v>
+            <v>300020</v>
           </cell>
           <cell r="B143" t="str">
-            <v>フォースライズ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300040</v>
+            <v>300030</v>
           </cell>
           <cell r="B144" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300050</v>
+            <v>300040</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ラピッドムーブ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300130</v>
+            <v>300050</v>
           </cell>
           <cell r="B146" t="str">
-            <v>アタックブレイク</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300140</v>
+            <v>300130</v>
           </cell>
           <cell r="B147" t="str">
-            <v>シールドバニッシュ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300210</v>
+            <v>300140</v>
           </cell>
           <cell r="B148" t="str">
-            <v>エーテルリチャージ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300220</v>
+            <v>300210</v>
           </cell>
           <cell r="B149" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300230</v>
+            <v>300220</v>
           </cell>
           <cell r="B150" t="str">
-            <v>ヴェンジェンス</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>301010</v>
+            <v>300230</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>301020</v>
+            <v>301010</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301030</v>
+            <v>301020</v>
           </cell>
           <cell r="B153" t="str">
-            <v>トライアングルガード</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301040</v>
+            <v>301030</v>
           </cell>
           <cell r="B154" t="str">
-            <v>セーフティバリア</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301050</v>
+            <v>301040</v>
           </cell>
           <cell r="B155" t="str">
-            <v>ヒロインズハイ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301060</v>
+            <v>301050</v>
           </cell>
           <cell r="B156" t="str">
-            <v>セカンドステージ</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301070</v>
+            <v>301060</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301080</v>
+            <v>301070</v>
           </cell>
           <cell r="B158" t="str">
-            <v>セプタブラスト</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301090</v>
+            <v>301080</v>
           </cell>
           <cell r="B159" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301100</v>
+            <v>301090</v>
           </cell>
           <cell r="B160" t="str">
-            <v>ファーストテイク</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>401010</v>
+            <v>301100</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ファイアボール+</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B162" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B163" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B165" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B166" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B167" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B168" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B169" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B170" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B172" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B173" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B174" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B175" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B176" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B177" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B178" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B179" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B180" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B182" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B183" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B184" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B185" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B188" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B189" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B190" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B191" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B196" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B199" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B202" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B203" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B204" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B205" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B206" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B208" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B209" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B210" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B211" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B212" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B213" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B214" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B215" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B216" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B218" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B219" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B220" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B221" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B222" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B223" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B224" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B225" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B226" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B227" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B237" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B238" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B239" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B240" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B242" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B243" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
+            <v>415080</v>
+          </cell>
+          <cell r="B245" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246">
             <v>415090</v>
           </cell>
-          <cell r="B245" t="str">
+          <cell r="B246" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -3488,22 +3496,22 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -3556,7 +3564,7 @@
         <v>13</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>11</v>
@@ -3609,7 +3617,7 @@
         <v>31</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -3662,13 +3670,13 @@
         <v>18</v>
       </c>
       <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>11</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
       </c>
       <c r="L5">
         <v>80</v>
@@ -3715,13 +3723,13 @@
         <v>32</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>11</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
       </c>
       <c r="L6">
         <v>60</v>
@@ -3768,7 +3776,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>11</v>
@@ -3821,13 +3829,13 @@
         <v>20</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
         <v>11</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
       </c>
       <c r="L8">
         <v>60</v>
@@ -3874,7 +3882,7 @@
         <v>14</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>11</v>
@@ -3927,7 +3935,7 @@
         <v>12</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>11</v>
@@ -3980,13 +3988,13 @@
         <v>31</v>
       </c>
       <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>5</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>11</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
       </c>
       <c r="L11">
         <v>50</v>
@@ -4033,7 +4041,7 @@
         <v>23</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>11</v>
@@ -4089,10 +4097,10 @@
         <v>1</v>
       </c>
       <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13">
         <v>11</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
       </c>
       <c r="L13">
         <v>80</v>
@@ -4139,13 +4147,13 @@
         <v>18</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
         <v>11</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4192,13 +4200,13 @@
         <v>11</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
         <v>11</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
       </c>
       <c r="L15">
         <v>110</v>
@@ -4245,7 +4253,7 @@
         <v>25</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>11</v>
@@ -4298,7 +4306,7 @@
         <v>12</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17">
         <v>11</v>
@@ -4351,13 +4359,13 @@
         <v>20</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
         <v>11</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
       </c>
       <c r="L18">
         <v>60</v>
@@ -4404,7 +4412,7 @@
         <v>14</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>11</v>
@@ -4457,7 +4465,7 @@
         <v>12</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20">
         <v>11</v>
@@ -4510,13 +4518,13 @@
         <v>31</v>
       </c>
       <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
         <v>5</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>11</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
       </c>
       <c r="L21">
         <v>50</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -469,8 +469,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -485,89 +485,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -589,6 +507,89 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -604,24 +605,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -642,13 +642,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,7 +672,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,43 +804,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,103 +816,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,6 +827,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -845,17 +860,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -886,24 +895,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -913,16 +904,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -935,7 +935,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -944,7 +944,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -953,127 +953,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1428,687 +1428,687 @@
         </row>
         <row r="34">
           <cell r="A34">
-            <v>4010</v>
+            <v>3120</v>
           </cell>
           <cell r="B34" t="str">
-            <v>セイントレーザー</v>
+            <v>ウォーターヒール</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="B35" t="str">
-            <v>ペネトレイト</v>
+            <v>セイントレーザー</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>4030</v>
+            <v>4020</v>
           </cell>
           <cell r="B36" t="str">
-            <v>ヒーリング</v>
+            <v>ペネトレイト</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>4040</v>
+            <v>4030</v>
           </cell>
           <cell r="B37" t="str">
-            <v>リザイアフォトン</v>
+            <v>ヒーリング</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>4050</v>
+            <v>4040</v>
           </cell>
           <cell r="B38" t="str">
-            <v>べネディクション</v>
+            <v>リザイアフォトン</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>4060</v>
+            <v>4050</v>
           </cell>
           <cell r="B39" t="str">
-            <v>ホーリーグレイス</v>
+            <v>べネディクション</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>4070</v>
+            <v>4060</v>
           </cell>
           <cell r="B40" t="str">
-            <v>キュアエール</v>
+            <v>ホーリーグレイス</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>4080</v>
+            <v>4070</v>
           </cell>
           <cell r="B41" t="str">
-            <v>ラインバリア</v>
+            <v>キュアエール</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>5010</v>
+            <v>4080</v>
           </cell>
           <cell r="B42" t="str">
-            <v>ダークプリズン</v>
+            <v>ラインバリア</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="B43" t="str">
-            <v>ユーサネイジア</v>
+            <v>ダークプリズン</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>5030</v>
+            <v>5020</v>
           </cell>
           <cell r="B44" t="str">
-            <v>ドレインヒール</v>
+            <v>ユーサネイジア</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>5040</v>
+            <v>5030</v>
           </cell>
           <cell r="B45" t="str">
-            <v>アビサルデスペア</v>
+            <v>ドレインヒール</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>5050</v>
+            <v>5040</v>
           </cell>
           <cell r="B46" t="str">
-            <v>ディプラヴィティ</v>
+            <v>アビサルデスペア</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>5060</v>
+            <v>5050</v>
           </cell>
           <cell r="B47" t="str">
-            <v>ダークネス</v>
+            <v>ディプラヴィティ</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>5070</v>
+            <v>5060</v>
           </cell>
           <cell r="B48" t="str">
-            <v>シェイディークラウド</v>
+            <v>ダークネス</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>5080</v>
+            <v>5070</v>
           </cell>
           <cell r="B49" t="str">
-            <v>ポイズンブロウ</v>
+            <v>シェイディークラウド</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>10010</v>
+            <v>5080</v>
           </cell>
           <cell r="B50" t="str">
-            <v>アンデッド</v>
+            <v>ポイズンブロウ</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>10020</v>
+            <v>10010</v>
           </cell>
           <cell r="B51" t="str">
-            <v>エアリアル</v>
+            <v>アンデッド</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>10030</v>
+            <v>10020</v>
           </cell>
           <cell r="B52" t="str">
-            <v>悪魔</v>
+            <v>エアリアル</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>10040</v>
+            <v>10030</v>
           </cell>
           <cell r="B53" t="str">
-            <v>クリーチャー</v>
+            <v>悪魔</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>10050</v>
+            <v>10040</v>
           </cell>
           <cell r="B54" t="str">
-            <v>野生の記憶</v>
+            <v>クリーチャー</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>10060</v>
+            <v>10050</v>
           </cell>
           <cell r="B55" t="str">
-            <v>変異生物</v>
+            <v>野生の記憶</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>11010</v>
+            <v>10060</v>
           </cell>
           <cell r="B56" t="str">
-            <v>ウルフソウル</v>
+            <v>変異生物</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>11020</v>
+            <v>11010</v>
           </cell>
           <cell r="B57" t="str">
-            <v>プリディカメント</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>11030</v>
+            <v>11020</v>
           </cell>
           <cell r="B58" t="str">
-            <v>アサルトシフト</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>11040</v>
+            <v>11030</v>
           </cell>
           <cell r="B59" t="str">
-            <v>アクティブギフト</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>11050</v>
+            <v>11040</v>
           </cell>
           <cell r="B60" t="str">
-            <v>イグナイテッド</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>11060</v>
+            <v>11050</v>
           </cell>
           <cell r="B61" t="str">
-            <v>ライジングファイア</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>11070</v>
+            <v>11060</v>
           </cell>
           <cell r="B62" t="str">
-            <v>ルージュバック</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>11080</v>
+            <v>11070</v>
           </cell>
           <cell r="B63" t="str">
-            <v>パワーエール</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>11090</v>
+            <v>11080</v>
           </cell>
           <cell r="B64" t="str">
-            <v>スレイプニル</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>12010</v>
+            <v>11090</v>
           </cell>
           <cell r="B65" t="str">
-            <v>エクステンション</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>12020</v>
+            <v>12010</v>
           </cell>
           <cell r="B66" t="str">
-            <v>ヘブンリーラック</v>
+            <v>エクステンション</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>12030</v>
+            <v>12020</v>
           </cell>
           <cell r="B67" t="str">
-            <v>スウィフトカレント</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>12040</v>
+            <v>12030</v>
           </cell>
           <cell r="B68" t="str">
-            <v>イヴェイドオール</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>12050</v>
+            <v>12040</v>
           </cell>
           <cell r="B69" t="str">
-            <v>クイックムーブ</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>12060</v>
+            <v>12050</v>
           </cell>
           <cell r="B70" t="str">
-            <v>チェイスマジック</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>12070</v>
+            <v>12060</v>
           </cell>
           <cell r="B71" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>12080</v>
+            <v>12070</v>
           </cell>
           <cell r="B72" t="str">
-            <v>ウィンドライズ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>12090</v>
+            <v>12080</v>
           </cell>
           <cell r="B73" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>13010</v>
+            <v>12090</v>
           </cell>
           <cell r="B74" t="str">
-            <v>アーマーコード</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>13020</v>
+            <v>13010</v>
           </cell>
           <cell r="B75" t="str">
-            <v>クイックバリア</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>13030</v>
+            <v>13020</v>
           </cell>
           <cell r="B76" t="str">
-            <v>クイックキュア</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>13040</v>
+            <v>13030</v>
           </cell>
           <cell r="B77" t="str">
-            <v>セルフシールド</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>13050</v>
+            <v>13040</v>
           </cell>
           <cell r="B78" t="str">
-            <v>パッシブジャミング</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>13060</v>
+            <v>13050</v>
           </cell>
           <cell r="B79" t="str">
-            <v>サプライカバー</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>13070</v>
+            <v>13060</v>
           </cell>
           <cell r="B80" t="str">
-            <v>アシッドラッシュ</v>
+            <v>サプライカバー</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>13080</v>
+            <v>13070</v>
           </cell>
           <cell r="B81" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>13090</v>
+            <v>13080</v>
           </cell>
           <cell r="B82" t="str">
-            <v>アイスセイバー</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>14010</v>
+            <v>13090</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ディバインシールド</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>14020</v>
+            <v>14010</v>
           </cell>
           <cell r="B84" t="str">
-            <v>ライフディバイド</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>14030</v>
+            <v>14020</v>
           </cell>
           <cell r="B85" t="str">
-            <v>エイミングスコープ</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>14040</v>
+            <v>14030</v>
           </cell>
           <cell r="B86" t="str">
-            <v>リジェネレーション</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>14050</v>
+            <v>14040</v>
           </cell>
           <cell r="B87" t="str">
-            <v>ホープフルアイリス</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>14060</v>
+            <v>14050</v>
           </cell>
           <cell r="B88" t="str">
-            <v>パッシブサプライ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>14070</v>
+            <v>14060</v>
           </cell>
           <cell r="B89" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>14080</v>
+            <v>14070</v>
           </cell>
           <cell r="B90" t="str">
-            <v>クイックヒール</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>14090</v>
+            <v>14080</v>
           </cell>
           <cell r="B91" t="str">
-            <v>リレイズ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>15010</v>
+            <v>14090</v>
           </cell>
           <cell r="B92" t="str">
-            <v>イーグルアイ</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>15020</v>
+            <v>15010</v>
           </cell>
           <cell r="B93" t="str">
-            <v>ネヴァーエンド</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>15030</v>
+            <v>15020</v>
           </cell>
           <cell r="B94" t="str">
-            <v>グレイブアクト</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>15040</v>
+            <v>15030</v>
           </cell>
           <cell r="B95" t="str">
-            <v>スカルグラッジ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>15050</v>
+            <v>15040</v>
           </cell>
           <cell r="B96" t="str">
-            <v>ネガティブドレイン</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>15060</v>
+            <v>15050</v>
           </cell>
           <cell r="B97" t="str">
-            <v>アンデッドペイン</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>15070</v>
+            <v>15060</v>
           </cell>
           <cell r="B98" t="str">
-            <v>ジャックポッド</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>15080</v>
+            <v>15070</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ヒールハント</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>15090</v>
+            <v>15080</v>
           </cell>
           <cell r="B100" t="str">
-            <v>クイックカース</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>20010</v>
+            <v>15090</v>
           </cell>
           <cell r="B101" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>100110</v>
+            <v>20010</v>
           </cell>
           <cell r="B102" t="str">
-            <v>ソーイングアームド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>100120</v>
+            <v>100110</v>
           </cell>
           <cell r="B103" t="str">
-            <v>エターナルロンド</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>100210</v>
+            <v>100120</v>
           </cell>
           <cell r="B104" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>100220</v>
+            <v>100210</v>
           </cell>
           <cell r="B105" t="str">
-            <v>レヴェリー</v>
+            <v>アブソリュートパリィ</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>100310</v>
+            <v>100220</v>
           </cell>
           <cell r="B106" t="str">
-            <v>セイクリッドバリア</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>100320</v>
+            <v>100310</v>
           </cell>
           <cell r="B107" t="str">
-            <v>リベンジニードル</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>100410</v>
+            <v>100320</v>
           </cell>
           <cell r="B108" t="str">
-            <v>アバンデンス</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>100420</v>
+            <v>100410</v>
           </cell>
           <cell r="B109" t="str">
-            <v>ハーヴェスト</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>100510</v>
+            <v>100420</v>
           </cell>
           <cell r="B110" t="str">
-            <v>カースドブレイク</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>100520</v>
+            <v>100510</v>
           </cell>
           <cell r="B111" t="str">
-            <v>ムーンライトレイ</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>100610</v>
+            <v>100520</v>
           </cell>
           <cell r="B112" t="str">
-            <v>サンフレイム</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>100620</v>
+            <v>100610</v>
           </cell>
           <cell r="B113" t="str">
-            <v>フレイムタン</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>100710</v>
+            <v>100620</v>
           </cell>
           <cell r="B114" t="str">
-            <v>ライズザフラッグ</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>100720</v>
+            <v>100710</v>
           </cell>
           <cell r="B115" t="str">
-            <v>オーバーリミット</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>100810</v>
+            <v>100720</v>
           </cell>
           <cell r="B116" t="str">
-            <v>テンパランス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>100820</v>
+            <v>100810</v>
           </cell>
           <cell r="B117" t="str">
-            <v>シエルクルセイダー</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>100910</v>
+            <v>100820</v>
           </cell>
           <cell r="B118" t="str">
-            <v>バーニングカウンター</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>100911</v>
+            <v>100910</v>
           </cell>
           <cell r="B119" t="str">
             <v>バーニングカウンター</v>
@@ -2116,15 +2116,15 @@
         </row>
         <row r="120">
           <cell r="A120">
-            <v>100920</v>
+            <v>100911</v>
           </cell>
           <cell r="B120" t="str">
-            <v>プロミネンス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>100921</v>
+            <v>100920</v>
           </cell>
           <cell r="B121" t="str">
             <v>プロミネンス</v>
@@ -2132,95 +2132,95 @@
         </row>
         <row r="122">
           <cell r="A122">
-            <v>101010</v>
+            <v>100921</v>
           </cell>
           <cell r="B122" t="str">
-            <v>エウロス</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>101020</v>
+            <v>101010</v>
           </cell>
           <cell r="B123" t="str">
-            <v>ボレアス</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>101110</v>
+            <v>101020</v>
           </cell>
           <cell r="B124" t="str">
-            <v>アバランシュ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>101120</v>
+            <v>101110</v>
           </cell>
           <cell r="B125" t="str">
-            <v>ブリザードコフィン</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>200210</v>
+            <v>101120</v>
           </cell>
           <cell r="B126" t="str">
-            <v>マイトレインフォース</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200220</v>
+            <v>200210</v>
           </cell>
           <cell r="B127" t="str">
-            <v>カタストロフィ</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200230</v>
+            <v>200220</v>
           </cell>
           <cell r="B128" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200310</v>
+            <v>200230</v>
           </cell>
           <cell r="B129" t="str">
-            <v>プルガシオン</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200320</v>
+            <v>200310</v>
           </cell>
           <cell r="B130" t="str">
-            <v>プリエステス</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200330</v>
+            <v>200320</v>
           </cell>
           <cell r="B131" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200410</v>
+            <v>200330</v>
           </cell>
           <cell r="B132" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200411</v>
+            <v>200410</v>
           </cell>
           <cell r="B133" t="str">
             <v>コウソクテンショウ</v>
@@ -2228,905 +2228,913 @@
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200420</v>
+            <v>200411</v>
           </cell>
           <cell r="B134" t="str">
-            <v>アンチバフ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200430</v>
+            <v>200420</v>
           </cell>
           <cell r="B135" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200510</v>
+            <v>200430</v>
           </cell>
           <cell r="B136" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200520</v>
+            <v>200510</v>
           </cell>
           <cell r="B137" t="str">
-            <v>グラウンドゼロ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200530</v>
+            <v>200520</v>
           </cell>
           <cell r="B138" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>201010</v>
+            <v>200530</v>
           </cell>
           <cell r="B139" t="str">
-            <v>カオスペイン</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201020</v>
+            <v>201010</v>
           </cell>
           <cell r="B140" t="str">
-            <v>フォールンワン</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>201030</v>
+            <v>201020</v>
           </cell>
           <cell r="B141" t="str">
-            <v>アンリマユ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>300010</v>
+            <v>201030</v>
           </cell>
           <cell r="B142" t="str">
-            <v>ライフブースト</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300020</v>
+            <v>300010</v>
           </cell>
           <cell r="B143" t="str">
-            <v>スピリットチャージ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300030</v>
+            <v>300020</v>
           </cell>
           <cell r="B144" t="str">
-            <v>フォースライズ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300040</v>
+            <v>300030</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300050</v>
+            <v>300040</v>
           </cell>
           <cell r="B146" t="str">
-            <v>ラピッドムーブ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300130</v>
+            <v>300050</v>
           </cell>
           <cell r="B147" t="str">
-            <v>アタックブレイク</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300140</v>
+            <v>300130</v>
           </cell>
           <cell r="B148" t="str">
-            <v>シールドバニッシュ</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300210</v>
+            <v>300140</v>
           </cell>
           <cell r="B149" t="str">
-            <v>エーテルリチャージ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300220</v>
+            <v>300210</v>
           </cell>
           <cell r="B150" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300230</v>
+            <v>300220</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ヴェンジェンス</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>301010</v>
+            <v>300230</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ディケイドリセット</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301020</v>
+            <v>301010</v>
           </cell>
           <cell r="B153" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301030</v>
+            <v>301020</v>
           </cell>
           <cell r="B154" t="str">
-            <v>トライアングルガード</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301040</v>
+            <v>301030</v>
           </cell>
           <cell r="B155" t="str">
-            <v>セーフティバリア</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301050</v>
+            <v>301040</v>
           </cell>
           <cell r="B156" t="str">
-            <v>ヒロインズハイ</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301060</v>
+            <v>301050</v>
           </cell>
           <cell r="B157" t="str">
-            <v>セカンドステージ</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301070</v>
+            <v>301060</v>
           </cell>
           <cell r="B158" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301080</v>
+            <v>301070</v>
           </cell>
           <cell r="B159" t="str">
-            <v>セプタブラスト</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301090</v>
+            <v>301080</v>
           </cell>
           <cell r="B160" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301100</v>
+            <v>301090</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ファーストテイク</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>401010</v>
+            <v>301100</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ファイアボール+</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B163" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B165" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B166" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B167" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B168" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B169" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B170" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B171" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B173" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B174" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B175" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B176" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B178" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B179" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B180" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B181" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B182" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B183" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B184" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B185" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B186" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B187" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B189" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B190" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B191" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B192" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B197" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B198" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B200" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B201" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B203" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B204" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B205" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B206" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B207" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B209" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B210" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B211" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B212" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B213" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B214" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B215" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B216" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B217" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B218" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B219" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B220" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B221" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B222" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B223" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B224" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B225" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B226" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B228" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B229" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B231" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B232" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B233" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B234" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B235" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B236" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B237" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B238" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B240" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B241" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B242" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B243" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B244" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B245" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
+            <v>415080</v>
+          </cell>
+          <cell r="B246" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247">
             <v>415090</v>
           </cell>
-          <cell r="B246" t="str">
+          <cell r="B247" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -469,15 +469,68 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -492,7 +545,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,75 +553,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -589,32 +574,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -624,6 +616,14 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -636,7 +636,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,19 +648,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,91 +714,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -774,7 +732,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,7 +744,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -798,25 +816,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -830,17 +830,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -860,20 +854,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -895,6 +886,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -907,23 +922,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -935,145 +935,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2172,969 +2172,993 @@
         </row>
         <row r="127">
           <cell r="A127">
-            <v>200210</v>
+            <v>200110</v>
           </cell>
           <cell r="B127" t="str">
-            <v>マイトレインフォース</v>
+            <v>アースクエイク</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>200220</v>
+            <v>200120</v>
           </cell>
           <cell r="B128" t="str">
-            <v>カタストロフィ</v>
+            <v>パワーレイズ</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>200230</v>
+            <v>200130</v>
           </cell>
           <cell r="B129" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>チャージ</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>200310</v>
+            <v>200210</v>
           </cell>
           <cell r="B130" t="str">
-            <v>プルガシオン</v>
+            <v>マイトレインフォース</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>200320</v>
+            <v>200220</v>
           </cell>
           <cell r="B131" t="str">
-            <v>プリエステス</v>
+            <v>カタストロフィ</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>200330</v>
+            <v>200230</v>
           </cell>
           <cell r="B132" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>200410</v>
+            <v>200310</v>
           </cell>
           <cell r="B133" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>200411</v>
+            <v>200320</v>
           </cell>
           <cell r="B134" t="str">
-            <v>コウソクテンショウ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>200420</v>
+            <v>200330</v>
           </cell>
           <cell r="B135" t="str">
-            <v>アンチバフ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>200430</v>
+            <v>200410</v>
           </cell>
           <cell r="B136" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>200510</v>
+            <v>200411</v>
           </cell>
           <cell r="B137" t="str">
-            <v>カウントダウン</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>200520</v>
+            <v>200420</v>
           </cell>
           <cell r="B138" t="str">
-            <v>グラウンドゼロ</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>200530</v>
+            <v>200430</v>
           </cell>
           <cell r="B139" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>201010</v>
+            <v>200510</v>
           </cell>
           <cell r="B140" t="str">
-            <v>カオスペイン</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>201020</v>
+            <v>200520</v>
           </cell>
           <cell r="B141" t="str">
-            <v>フォールンワン</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>201030</v>
+            <v>200530</v>
           </cell>
           <cell r="B142" t="str">
-            <v>アンリマユ</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>300010</v>
+            <v>201010</v>
           </cell>
           <cell r="B143" t="str">
-            <v>ライフブースト</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>300020</v>
+            <v>201020</v>
           </cell>
           <cell r="B144" t="str">
-            <v>スピリットチャージ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>300030</v>
+            <v>201030</v>
           </cell>
           <cell r="B145" t="str">
-            <v>フォースライズ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>300040</v>
+            <v>300010</v>
           </cell>
           <cell r="B146" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>300050</v>
+            <v>300020</v>
           </cell>
           <cell r="B147" t="str">
-            <v>ラピッドムーブ</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>300130</v>
+            <v>300030</v>
           </cell>
           <cell r="B148" t="str">
-            <v>アタックブレイク</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>300140</v>
+            <v>300040</v>
           </cell>
           <cell r="B149" t="str">
-            <v>シールドバニッシュ</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>300210</v>
+            <v>300050</v>
           </cell>
           <cell r="B150" t="str">
-            <v>エーテルリチャージ</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>300220</v>
+            <v>300130</v>
           </cell>
           <cell r="B151" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>300230</v>
+            <v>300140</v>
           </cell>
           <cell r="B152" t="str">
-            <v>ヴェンジェンス</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>301010</v>
+            <v>300210</v>
           </cell>
           <cell r="B153" t="str">
-            <v>ディケイドリセット</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>301020</v>
+            <v>300220</v>
           </cell>
           <cell r="B154" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>301030</v>
+            <v>300230</v>
           </cell>
           <cell r="B155" t="str">
-            <v>トライアングルガード</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>301040</v>
+            <v>301010</v>
           </cell>
           <cell r="B156" t="str">
-            <v>セーフティバリア</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>301050</v>
+            <v>301020</v>
           </cell>
           <cell r="B157" t="str">
-            <v>ヒロインズハイ</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>301060</v>
+            <v>301030</v>
           </cell>
           <cell r="B158" t="str">
-            <v>セカンドステージ</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>301070</v>
+            <v>301040</v>
           </cell>
           <cell r="B159" t="str">
-            <v>ハイヒットポイント</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>301080</v>
+            <v>301050</v>
           </cell>
           <cell r="B160" t="str">
-            <v>セプタブラスト</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>301090</v>
+            <v>301060</v>
           </cell>
           <cell r="B161" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>301100</v>
+            <v>301070</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ファーストテイク</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>401010</v>
+            <v>301080</v>
           </cell>
           <cell r="B163" t="str">
-            <v>ファイアボール+</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>401020</v>
+            <v>301090</v>
           </cell>
           <cell r="B164" t="str">
-            <v>バーンストーム+</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>401030</v>
+            <v>301100</v>
           </cell>
           <cell r="B165" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>401040</v>
+            <v>401010</v>
           </cell>
           <cell r="B166" t="str">
-            <v>ソードアダプト+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>401050</v>
+            <v>401020</v>
           </cell>
           <cell r="B167" t="str">
-            <v>フレイムレイン+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>401060</v>
+            <v>401030</v>
           </cell>
           <cell r="B168" t="str">
-            <v>イクスティンクション+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>401070</v>
+            <v>401040</v>
           </cell>
           <cell r="B169" t="str">
-            <v>バーニングソウル+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>401080</v>
+            <v>401050</v>
           </cell>
           <cell r="B170" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>402010</v>
+            <v>401060</v>
           </cell>
           <cell r="B171" t="str">
-            <v>ディスチャージ+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>402020</v>
+            <v>401070</v>
           </cell>
           <cell r="B172" t="str">
-            <v>イベイドコード+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>402030</v>
+            <v>401080</v>
           </cell>
           <cell r="B173" t="str">
-            <v>ショックインパルス+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402040</v>
+            <v>402010</v>
           </cell>
           <cell r="B174" t="str">
-            <v>トラストチェイン+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>402050</v>
+            <v>402020</v>
           </cell>
           <cell r="B175" t="str">
-            <v>スペルバニシング+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>402060</v>
+            <v>402030</v>
           </cell>
           <cell r="B176" t="str">
-            <v>アーテニーストライク+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>402070</v>
+            <v>402040</v>
           </cell>
           <cell r="B177" t="str">
-            <v>コンセントレイト+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>402080</v>
+            <v>402050</v>
           </cell>
           <cell r="B178" t="str">
-            <v>ディレイマジック+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>403010</v>
+            <v>402060</v>
           </cell>
           <cell r="B179" t="str">
-            <v>アイスブレイド+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>403020</v>
+            <v>402070</v>
           </cell>
           <cell r="B180" t="str">
-            <v>カウンターオーラ+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>403030</v>
+            <v>402080</v>
           </cell>
           <cell r="B181" t="str">
-            <v>ラインプロテクト+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>403040</v>
+            <v>403010</v>
           </cell>
           <cell r="B182" t="str">
-            <v>エスコートソール+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>403050</v>
+            <v>403020</v>
           </cell>
           <cell r="B183" t="str">
-            <v>ディープフリーズ+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>403060</v>
+            <v>403030</v>
           </cell>
           <cell r="B184" t="str">
-            <v>バブルブロウ+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>403070</v>
+            <v>403040</v>
           </cell>
           <cell r="B185" t="str">
-            <v>アクアミラージュ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>403080</v>
+            <v>403050</v>
           </cell>
           <cell r="B186" t="str">
-            <v>フロストシールド+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>404010</v>
+            <v>403060</v>
           </cell>
           <cell r="B187" t="str">
-            <v>セイントレーザー+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>404020</v>
+            <v>403070</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ペネトレイト+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>404030</v>
+            <v>403080</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ヒーリング+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>404040</v>
+            <v>404010</v>
           </cell>
           <cell r="B190" t="str">
-            <v>リザイアフォトン+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>404050</v>
+            <v>404020</v>
           </cell>
           <cell r="B191" t="str">
-            <v>べネディクション+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>404060</v>
+            <v>404030</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>404070</v>
+            <v>404040</v>
           </cell>
           <cell r="B193" t="str">
-            <v>キュアエール+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>404080</v>
+            <v>404050</v>
           </cell>
           <cell r="B194" t="str">
-            <v>ラインバリア+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>405010</v>
+            <v>404060</v>
           </cell>
           <cell r="B195" t="str">
-            <v>ダークプリズン+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>405020</v>
+            <v>404070</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ユーサネイジア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>405030</v>
+            <v>404080</v>
           </cell>
           <cell r="B197" t="str">
-            <v>ドレインヒール+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>405040</v>
+            <v>405010</v>
           </cell>
           <cell r="B198" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>405050</v>
+            <v>405020</v>
           </cell>
           <cell r="B199" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>405060</v>
+            <v>405030</v>
           </cell>
           <cell r="B200" t="str">
-            <v>ダークネス+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>405070</v>
+            <v>405040</v>
           </cell>
           <cell r="B201" t="str">
-            <v>シェイディークラウド+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>405080</v>
+            <v>405050</v>
           </cell>
           <cell r="B202" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>411010</v>
+            <v>405060</v>
           </cell>
           <cell r="B203" t="str">
-            <v>ウルフソウル+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>411020</v>
+            <v>405070</v>
           </cell>
           <cell r="B204" t="str">
-            <v>プリディカメント+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>411030</v>
+            <v>405080</v>
           </cell>
           <cell r="B205" t="str">
-            <v>アサルトシフト+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>411040</v>
+            <v>411010</v>
           </cell>
           <cell r="B206" t="str">
-            <v>アクティブギフト+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>411050</v>
+            <v>411020</v>
           </cell>
           <cell r="B207" t="str">
-            <v>イグナイテッド+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>411060</v>
+            <v>411030</v>
           </cell>
           <cell r="B208" t="str">
-            <v>ライジングファイア+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>411070</v>
+            <v>411040</v>
           </cell>
           <cell r="B209" t="str">
-            <v>ルージュバック+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>411080</v>
+            <v>411050</v>
           </cell>
           <cell r="B210" t="str">
-            <v>パワーエール+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>411090</v>
+            <v>411060</v>
           </cell>
           <cell r="B211" t="str">
-            <v>スレイプニル+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>412010</v>
+            <v>411070</v>
           </cell>
           <cell r="B212" t="str">
-            <v>エクステンション+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>412020</v>
+            <v>411080</v>
           </cell>
           <cell r="B213" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>412030</v>
+            <v>411090</v>
           </cell>
           <cell r="B214" t="str">
-            <v>スウィフトカレント+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>412040</v>
+            <v>412010</v>
           </cell>
           <cell r="B215" t="str">
-            <v>イヴェイドオール+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>412050</v>
+            <v>412020</v>
           </cell>
           <cell r="B216" t="str">
-            <v>クイックムーブ+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>412060</v>
+            <v>412030</v>
           </cell>
           <cell r="B217" t="str">
-            <v>チェイスマジック+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>412070</v>
+            <v>412040</v>
           </cell>
           <cell r="B218" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>412080</v>
+            <v>412050</v>
           </cell>
           <cell r="B219" t="str">
-            <v>ウィンドライズ+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>412090</v>
+            <v>412060</v>
           </cell>
           <cell r="B220" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>413010</v>
+            <v>412070</v>
           </cell>
           <cell r="B221" t="str">
-            <v>アーマーコード+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>413020</v>
+            <v>412080</v>
           </cell>
           <cell r="B222" t="str">
-            <v>クイックバリア+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>413030</v>
+            <v>412090</v>
           </cell>
           <cell r="B223" t="str">
-            <v>クイックキュア+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>413040</v>
+            <v>413010</v>
           </cell>
           <cell r="B224" t="str">
-            <v>セルフシールド+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>413050</v>
+            <v>413020</v>
           </cell>
           <cell r="B225" t="str">
-            <v>パッシブジャミング+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>413060</v>
+            <v>413030</v>
           </cell>
           <cell r="B226" t="str">
-            <v>サプライカバー+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>413070</v>
+            <v>413040</v>
           </cell>
           <cell r="B227" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>413080</v>
+            <v>413050</v>
           </cell>
           <cell r="B228" t="str">
-            <v>ライフスティール+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>413090</v>
+            <v>413060</v>
           </cell>
           <cell r="B229" t="str">
-            <v>アイスセイバー+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>414010</v>
+            <v>413070</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ディバインシールド+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>414020</v>
+            <v>413080</v>
           </cell>
           <cell r="B231" t="str">
-            <v>ライフディバイド+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>414030</v>
+            <v>413090</v>
           </cell>
           <cell r="B232" t="str">
-            <v>エイミングスコープ+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>414040</v>
+            <v>414010</v>
           </cell>
           <cell r="B233" t="str">
-            <v>リジェネレーション+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>414050</v>
+            <v>414020</v>
           </cell>
           <cell r="B234" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>414060</v>
+            <v>414030</v>
           </cell>
           <cell r="B235" t="str">
-            <v>パッシブサプライ+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>414070</v>
+            <v>414040</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>414080</v>
+            <v>414050</v>
           </cell>
           <cell r="B237" t="str">
-            <v>クイックヒール+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>414090</v>
+            <v>414060</v>
           </cell>
           <cell r="B238" t="str">
-            <v>リレイズ+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>415010</v>
+            <v>414070</v>
           </cell>
           <cell r="B239" t="str">
-            <v>イーグルアイ+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>415020</v>
+            <v>414080</v>
           </cell>
           <cell r="B240" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>415030</v>
+            <v>414090</v>
           </cell>
           <cell r="B241" t="str">
-            <v>グレイブアクト+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>415040</v>
+            <v>415010</v>
           </cell>
           <cell r="B242" t="str">
-            <v>スカルグラッジ+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>415050</v>
+            <v>415020</v>
           </cell>
           <cell r="B243" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>415060</v>
+            <v>415030</v>
           </cell>
           <cell r="B244" t="str">
-            <v>アンデッドペイン+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>415070</v>
+            <v>415040</v>
           </cell>
           <cell r="B245" t="str">
-            <v>ジャックポッド+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>415080</v>
+            <v>415050</v>
           </cell>
           <cell r="B246" t="str">
-            <v>ヒールハント+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
+            <v>415060</v>
+          </cell>
+          <cell r="B247" t="str">
+            <v>アンデッドペイン+</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248">
+            <v>415070</v>
+          </cell>
+          <cell r="B248" t="str">
+            <v>ジャックポッド+</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249">
+            <v>415080</v>
+          </cell>
+          <cell r="B249" t="str">
+            <v>ヒールハント+</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250">
             <v>415090</v>
           </cell>
-          <cell r="B247" t="str">
+          <cell r="B250" t="str">
             <v>クイックカース+</v>
           </cell>
         </row>
@@ -5944,7 +5968,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -7791,7 +7815,7 @@
         <v>50</v>
       </c>
       <c r="F77">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7799,23 +7823,23 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B78">
-        <v>5010</v>
+        <v>1020</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>バーンストーム</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>9031</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7823,20 +7847,20 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79">
-        <v>15050</v>
+        <v>200110</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アースクエイク</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -7847,20 +7871,20 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80">
-        <v>200210</v>
+        <v>200120</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>パワーレイズ</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -7871,20 +7895,20 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81">
-        <v>200220</v>
+        <v>200130</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>チャージ</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -7898,17 +7922,17 @@
         <v>102</v>
       </c>
       <c r="B82">
-        <v>200230</v>
+        <v>5010</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -7919,20 +7943,20 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B83">
-        <v>4010</v>
+        <v>15050</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -7943,23 +7967,23 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B84">
-        <v>4030</v>
+        <v>200210</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -7967,23 +7991,23 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85">
-        <v>14080</v>
+        <v>200220</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F85">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -7991,14 +8015,14 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B86">
-        <v>200310</v>
+        <v>200230</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -8018,17 +8042,17 @@
         <v>103</v>
       </c>
       <c r="B87">
-        <v>200320</v>
+        <v>4010</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -8042,20 +8066,20 @@
         <v>103</v>
       </c>
       <c r="B88">
-        <v>200330</v>
+        <v>4030</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8063,23 +8087,23 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B89">
-        <v>2010</v>
+        <v>14080</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8087,14 +8111,14 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B90">
-        <v>200410</v>
+        <v>200310</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -8111,23 +8135,23 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B91">
-        <v>200420</v>
+        <v>200320</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>プリエステス</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F91">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8135,14 +8159,14 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B92">
-        <v>200430</v>
+        <v>200330</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -8159,20 +8183,20 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B93">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -8183,20 +8207,20 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B94">
-        <v>3070</v>
+        <v>200410</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -8207,14 +8231,14 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B95">
-        <v>200510</v>
+        <v>200420</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -8223,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -8231,20 +8255,20 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B96">
-        <v>200520</v>
+        <v>200430</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -8258,17 +8282,17 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>200530</v>
+        <v>3010</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -8282,17 +8306,17 @@
         <v>105</v>
       </c>
       <c r="B98">
-        <v>403070</v>
+        <v>3070</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -8303,20 +8327,20 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B99">
-        <v>5010</v>
+        <v>200510</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -8327,14 +8351,14 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B100">
-        <v>5020</v>
+        <v>200520</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -8351,23 +8375,23 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B101">
-        <v>3070</v>
+        <v>200530</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>9110</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -8375,7 +8399,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B102">
         <v>403070</v>
@@ -8402,20 +8426,20 @@
         <v>201</v>
       </c>
       <c r="B103">
-        <v>201010</v>
+        <v>5010</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F103">
-        <v>5080</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -8426,17 +8450,17 @@
         <v>201</v>
       </c>
       <c r="B104">
-        <v>201020</v>
+        <v>5020</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -8450,20 +8474,20 @@
         <v>201</v>
       </c>
       <c r="B105">
-        <v>201030</v>
+        <v>3070</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>9110</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -8474,11 +8498,11 @@
         <v>201</v>
       </c>
       <c r="B106">
-        <v>405010</v>
+        <v>403070</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -8498,11 +8522,11 @@
         <v>201</v>
       </c>
       <c r="B107">
-        <v>405020</v>
+        <v>201010</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>カオスペイン</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -8511,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>5080</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -8522,17 +8546,17 @@
         <v>201</v>
       </c>
       <c r="B108">
-        <v>12010</v>
+        <v>201020</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>フォールンワン</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -8543,23 +8567,23 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B109">
-        <v>1010</v>
+        <v>201030</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>アンリマユ</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -8567,23 +8591,23 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B110">
-        <v>1060</v>
+        <v>405010</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8591,14 +8615,14 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B111">
-        <v>100110</v>
+        <v>405020</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -8615,20 +8639,20 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B112">
-        <v>100120</v>
+        <v>12010</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>エクステンション</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -8642,20 +8666,20 @@
         <v>1001</v>
       </c>
       <c r="B113">
-        <v>11060</v>
+        <v>1010</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -8666,20 +8690,20 @@
         <v>1001</v>
       </c>
       <c r="B114">
-        <v>14010</v>
+        <v>1060</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -8690,11 +8714,11 @@
         <v>1001</v>
       </c>
       <c r="B115">
-        <v>12010</v>
+        <v>100110</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -8714,17 +8738,17 @@
         <v>1001</v>
       </c>
       <c r="B116">
-        <v>12060</v>
+        <v>100120</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -8735,23 +8759,23 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B117">
-        <v>2010</v>
+        <v>11060</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -8759,20 +8783,20 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B118">
-        <v>2070</v>
+        <v>14010</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -8783,14 +8807,14 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B119">
-        <v>100210</v>
+        <v>12010</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>エクステンション</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -8807,26 +8831,26 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B120">
-        <v>100220</v>
+        <v>12060</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -8834,20 +8858,20 @@
         <v>1002</v>
       </c>
       <c r="B121">
-        <v>402070</v>
+        <v>2010</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -8858,17 +8882,17 @@
         <v>1002</v>
       </c>
       <c r="B122">
-        <v>12080</v>
+        <v>2070</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -8882,11 +8906,11 @@
         <v>1002</v>
       </c>
       <c r="B123">
-        <v>12040</v>
+        <v>100210</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -8906,23 +8930,23 @@
         <v>1002</v>
       </c>
       <c r="B124">
-        <v>12050</v>
+        <v>100220</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -8930,11 +8954,11 @@
         <v>1002</v>
       </c>
       <c r="B125">
-        <v>12010</v>
+        <v>402070</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -8951,20 +8975,20 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B126">
-        <v>3010</v>
+        <v>12080</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -8975,23 +8999,23 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B127">
-        <v>3020</v>
+        <v>12040</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>カウンターオーラ</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -8999,14 +9023,14 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B128">
-        <v>100310</v>
+        <v>12050</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -9023,23 +9047,23 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B129">
-        <v>100320</v>
+        <v>12010</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>エクステンション</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F129">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9050,17 +9074,17 @@
         <v>1003</v>
       </c>
       <c r="B130">
-        <v>403020</v>
+        <v>3010</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -9074,20 +9098,20 @@
         <v>1003</v>
       </c>
       <c r="B131">
-        <v>403010</v>
+        <v>3020</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>カウンターオーラ</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -9098,11 +9122,11 @@
         <v>1003</v>
       </c>
       <c r="B132">
-        <v>13020</v>
+        <v>100310</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -9122,20 +9146,20 @@
         <v>1003</v>
       </c>
       <c r="B133">
-        <v>13080</v>
+        <v>100320</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D133">
         <v>1</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -9146,11 +9170,11 @@
         <v>1003</v>
       </c>
       <c r="B134">
-        <v>14050</v>
+        <v>403020</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -9167,20 +9191,20 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B135">
-        <v>4010</v>
+        <v>403010</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -9191,23 +9215,23 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B136">
-        <v>4030</v>
+        <v>13020</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -9215,14 +9239,14 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B137">
-        <v>100410</v>
+        <v>13080</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -9239,20 +9263,20 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B138">
-        <v>100420</v>
+        <v>14050</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -9266,17 +9290,17 @@
         <v>1004</v>
       </c>
       <c r="B139">
-        <v>404030</v>
+        <v>4010</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9290,20 +9314,20 @@
         <v>1004</v>
       </c>
       <c r="B140">
-        <v>14080</v>
+        <v>4030</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -9314,11 +9338,11 @@
         <v>1004</v>
       </c>
       <c r="B141">
-        <v>14010</v>
+        <v>100410</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -9327,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -9338,17 +9362,17 @@
         <v>1004</v>
       </c>
       <c r="B142">
-        <v>14040</v>
+        <v>100420</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -9362,11 +9386,11 @@
         <v>1004</v>
       </c>
       <c r="B143">
-        <v>14090</v>
+        <v>404030</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -9383,20 +9407,20 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B144">
-        <v>5010</v>
+        <v>14080</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -9407,23 +9431,23 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B145">
-        <v>5070</v>
+        <v>14010</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>5061</v>
+        <v>1023</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -9431,14 +9455,14 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B146">
-        <v>100510</v>
+        <v>14040</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -9455,20 +9479,20 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B147">
-        <v>100520</v>
+        <v>14090</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>リレイズ</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -9482,17 +9506,17 @@
         <v>1005</v>
       </c>
       <c r="B148">
-        <v>15090</v>
+        <v>5010</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9506,20 +9530,20 @@
         <v>1005</v>
       </c>
       <c r="B149">
-        <v>405070</v>
+        <v>5070</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -9530,11 +9554,11 @@
         <v>1005</v>
       </c>
       <c r="B150">
-        <v>15080</v>
+        <v>100510</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -9554,17 +9578,17 @@
         <v>1005</v>
       </c>
       <c r="B151">
-        <v>405010</v>
+        <v>100520</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -9578,11 +9602,11 @@
         <v>1005</v>
       </c>
       <c r="B152">
-        <v>415090</v>
+        <v>15090</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>クイックカース</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -9599,20 +9623,20 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B153">
-        <v>1010</v>
+        <v>405070</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -9623,47 +9647,47 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B154">
-        <v>1030</v>
+        <v>15080</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F154">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B155">
-        <v>1070</v>
+        <v>405010</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -9671,14 +9695,14 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B156">
-        <v>100610</v>
+        <v>415090</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -9698,17 +9722,17 @@
         <v>1006</v>
       </c>
       <c r="B157">
-        <v>100620</v>
+        <v>1010</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -9722,23 +9746,23 @@
         <v>1006</v>
       </c>
       <c r="B158">
-        <v>11040</v>
+        <v>1030</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>ヒートスタンプ</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F158">
-        <v>5042</v>
+        <v>9120</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -9746,20 +9770,20 @@
         <v>1006</v>
       </c>
       <c r="B159">
-        <v>401030</v>
+        <v>1070</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -9770,11 +9794,11 @@
         <v>1006</v>
       </c>
       <c r="B160">
-        <v>411040</v>
+        <v>100610</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -9794,17 +9818,17 @@
         <v>1006</v>
       </c>
       <c r="B161">
-        <v>13040</v>
+        <v>100620</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -9815,23 +9839,23 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B162">
-        <v>2010</v>
+        <v>11040</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -9839,23 +9863,23 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B163">
-        <v>2040</v>
+        <v>401030</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -9863,14 +9887,14 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B164">
-        <v>100710</v>
+        <v>411040</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -9887,20 +9911,20 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B165">
-        <v>100720</v>
+        <v>13040</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -9914,20 +9938,20 @@
         <v>1007</v>
       </c>
       <c r="B166">
-        <v>12090</v>
+        <v>2010</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F166">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -9938,20 +9962,20 @@
         <v>1007</v>
       </c>
       <c r="B167">
-        <v>412090</v>
+        <v>2040</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -9962,11 +9986,11 @@
         <v>1007</v>
       </c>
       <c r="B168">
-        <v>12050</v>
+        <v>100710</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -9986,17 +10010,17 @@
         <v>1007</v>
       </c>
       <c r="B169">
-        <v>12070</v>
+        <v>100720</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D169">
         <v>1</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -10010,11 +10034,11 @@
         <v>1007</v>
       </c>
       <c r="B170">
-        <v>14030</v>
+        <v>12090</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -10023,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G170">
         <v>0</v>
@@ -10031,20 +10055,20 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B171">
-        <v>3010</v>
+        <v>412090</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -10055,20 +10079,20 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B172">
-        <v>3070</v>
+        <v>12050</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -10079,14 +10103,14 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B173">
-        <v>100810</v>
+        <v>12070</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -10103,20 +10127,20 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B174">
-        <v>100820</v>
+        <v>14030</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D174">
         <v>1</v>
       </c>
       <c r="E174">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -10130,20 +10154,20 @@
         <v>1008</v>
       </c>
       <c r="B175">
-        <v>13060</v>
+        <v>3010</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F175">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -10154,17 +10178,17 @@
         <v>1008</v>
       </c>
       <c r="B176">
-        <v>403070</v>
+        <v>3070</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -10178,11 +10202,11 @@
         <v>1008</v>
       </c>
       <c r="B177">
-        <v>13010</v>
+        <v>100810</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>テンパランス</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -10202,17 +10226,17 @@
         <v>1008</v>
       </c>
       <c r="B178">
-        <v>13020</v>
+        <v>100820</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -10226,11 +10250,11 @@
         <v>1008</v>
       </c>
       <c r="B179">
-        <v>13040</v>
+        <v>13060</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>サプライカバー</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -10239,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -10247,20 +10271,20 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B180">
-        <v>1010</v>
+        <v>403070</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -10271,23 +10295,23 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B181">
-        <v>1050</v>
+        <v>13010</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -10295,14 +10319,14 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B182">
-        <v>100910</v>
+        <v>13020</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -10319,20 +10343,20 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B183">
-        <v>100920</v>
+        <v>13040</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -10346,17 +10370,17 @@
         <v>1009</v>
       </c>
       <c r="B184">
-        <v>11070</v>
+        <v>1010</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -10370,20 +10394,20 @@
         <v>1009</v>
       </c>
       <c r="B185">
-        <v>401050</v>
+        <v>1050</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G185">
         <v>0</v>
@@ -10394,11 +10418,11 @@
         <v>1009</v>
       </c>
       <c r="B186">
-        <v>11030</v>
+        <v>100910</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -10418,17 +10442,17 @@
         <v>1009</v>
       </c>
       <c r="B187">
-        <v>11020</v>
+        <v>100920</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -10442,11 +10466,11 @@
         <v>1009</v>
       </c>
       <c r="B188">
-        <v>15040</v>
+        <v>11070</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -10463,20 +10487,20 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B189">
-        <v>2010</v>
+        <v>401050</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -10487,23 +10511,23 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B190">
-        <v>2030</v>
+        <v>11030</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>ショックインパルス</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F190">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -10511,14 +10535,14 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B191">
-        <v>101010</v>
+        <v>11020</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>プリディカメント</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -10535,20 +10559,20 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B192">
-        <v>101020</v>
+        <v>15040</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -10562,17 +10586,17 @@
         <v>1010</v>
       </c>
       <c r="B193">
-        <v>12010</v>
+        <v>2010</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -10586,20 +10610,20 @@
         <v>1010</v>
       </c>
       <c r="B194">
-        <v>402030</v>
+        <v>2030</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ショックインパルス</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -10610,11 +10634,11 @@
         <v>1010</v>
       </c>
       <c r="B195">
-        <v>12020</v>
+        <v>101010</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>エウロス</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -10634,17 +10658,17 @@
         <v>1010</v>
       </c>
       <c r="B196">
-        <v>12030</v>
+        <v>101020</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ボレアス</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -10658,11 +10682,11 @@
         <v>1010</v>
       </c>
       <c r="B197">
-        <v>15070</v>
+        <v>12010</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>エクステンション</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -10679,20 +10703,20 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B198">
-        <v>3010</v>
+        <v>402030</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -10703,20 +10727,20 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B199">
-        <v>3050</v>
+        <v>12020</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -10727,14 +10751,14 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B200">
-        <v>101110</v>
+        <v>12030</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -10751,20 +10775,20 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B201">
-        <v>101120</v>
+        <v>15070</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -10778,17 +10802,17 @@
         <v>1011</v>
       </c>
       <c r="B202">
-        <v>13090</v>
+        <v>3010</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -10802,17 +10826,17 @@
         <v>1011</v>
       </c>
       <c r="B203">
-        <v>403050</v>
+        <v>3050</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -10826,11 +10850,11 @@
         <v>1011</v>
       </c>
       <c r="B204">
-        <v>13050</v>
+        <v>101110</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -10850,17 +10874,17 @@
         <v>1011</v>
       </c>
       <c r="B205">
-        <v>13070</v>
+        <v>101120</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -10874,22 +10898,118 @@
         <v>1011</v>
       </c>
       <c r="B206">
-        <v>14070</v>
+        <v>13090</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
+        <v>アイスセイバー</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207">
+        <v>1011</v>
+      </c>
+      <c r="B207">
+        <v>403050</v>
+      </c>
+      <c r="C207" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208">
+        <v>1011</v>
+      </c>
+      <c r="B208">
+        <v>13050</v>
+      </c>
+      <c r="C208" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
+        <v>パッシブジャミング</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209">
+        <v>1011</v>
+      </c>
+      <c r="B209">
+        <v>13070</v>
+      </c>
+      <c r="C209" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210">
+        <v>1011</v>
+      </c>
+      <c r="B210">
+        <v>14070</v>
+      </c>
+      <c r="C210" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D206">
-        <v>1</v>
-      </c>
-      <c r="E206">
-        <v>0</v>
-      </c>
-      <c r="F206">
-        <v>0</v>
-      </c>
-      <c r="G206">
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
         <v>0</v>
       </c>
     </row>
@@ -10902,7 +11022,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -11091,19 +11211,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B9">
-        <v>1040</v>
+        <v>2050</v>
       </c>
       <c r="C9">
-        <v>4020</v>
+        <v>1020</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -11114,25 +11234,25 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10">
-        <v>2050</v>
+        <v>1040</v>
       </c>
       <c r="C10">
-        <v>1020</v>
+        <v>4020</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -11143,64 +11263,41 @@
         <v>1040</v>
       </c>
       <c r="C11">
-        <v>4020</v>
+        <v>1020</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12">
-        <v>1040</v>
+        <v>4050</v>
       </c>
       <c r="C12">
-        <v>1020</v>
+        <v>4020</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>105</v>
-      </c>
-      <c r="B13">
-        <v>4050</v>
-      </c>
-      <c r="C13">
-        <v>4020</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -470,9 +470,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -483,71 +483,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -566,6 +506,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,9 +542,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -591,9 +566,48 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -605,22 +619,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -636,7 +636,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,7 +654,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,37 +684,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,13 +702,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,43 +750,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -774,13 +780,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -792,31 +816,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,15 +827,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -854,6 +845,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -865,21 +867,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -910,11 +897,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -935,145 +935,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
